--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,1374 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131647724</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471234</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6538627</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnag</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131647743</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471233</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6538625</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131648006</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97901</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471183</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6538699</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131648085</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97898</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471169</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6538704</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131648678</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97901</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471211</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6538658</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131647499</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471235</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6538598</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>131647594</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471229</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6538600</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>131647812</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57086</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471182</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6538683</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Satt I träd och flög norrut.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>131648688</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97898</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>471211</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6538655</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131648564</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471253</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6538764</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen av död avbruten gran</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131647894</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>471180</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6538698</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med färska ringhack på hela tallen, märkt med rött band</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131647961</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57898</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>471176</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6538685</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med ringhack med savflöde på tall märkt med rött märkband</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B5" t="n">
-        <v>97901</v>
+        <v>97898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R5" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648085</v>
+        <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>97898</v>
+        <v>97901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471169</v>
+        <v>471183</v>
       </c>
       <c r="R6" t="n">
-        <v>6538704</v>
+        <v>6538699</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -1023,7 +1023,7 @@
         <v>131648085</v>
       </c>
       <c r="B5" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>97901</v>
+        <v>97902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97901</v>
+        <v>97902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>131648688</v>
       </c>
       <c r="B11" t="n">
-        <v>97898</v>
+        <v>97899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131647724</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>5198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131648085</v>
       </c>
       <c r="B4" t="n">
-        <v>57895</v>
+        <v>97900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471169</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538704</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648085</v>
+        <v>131648006</v>
       </c>
       <c r="B5" t="n">
-        <v>97899</v>
+        <v>97903</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1021,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471169</v>
+        <v>471183</v>
       </c>
       <c r="R5" t="n">
-        <v>6538704</v>
+        <v>6538699</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,45 +1117,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B6" t="n">
-        <v>97902</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R6" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97902</v>
+        <v>97903</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>131647594</v>
       </c>
       <c r="B9" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>131647812</v>
       </c>
       <c r="B10" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>131648688</v>
       </c>
       <c r="B11" t="n">
-        <v>97899</v>
+        <v>97900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,45 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>97900</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R4" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B5" t="n">
         <v>97903</v>
@@ -1021,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R5" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1080,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,50 +1127,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>97906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R6" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97903</v>
+        <v>97906</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,50 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647499</v>
+        <v>131648688</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>97903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471235</v>
+        <v>471211</v>
       </c>
       <c r="R8" t="n">
-        <v>6538598</v>
+        <v>6538655</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,38 +1448,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647594</v>
+        <v>131647812</v>
       </c>
       <c r="B9" t="n">
-        <v>57896</v>
+        <v>57090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1498,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471182</v>
       </c>
       <c r="R9" t="n">
-        <v>6538600</v>
+        <v>6538683</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,47 +1574,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647812</v>
+        <v>131647499</v>
       </c>
       <c r="B10" t="n">
-        <v>57087</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471182</v>
+        <v>471235</v>
       </c>
       <c r="R10" t="n">
-        <v>6538683</v>
+        <v>6538598</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1659,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,45 +1691,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131648688</v>
+        <v>131647594</v>
       </c>
       <c r="B11" t="n">
-        <v>97900</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471211</v>
+        <v>471229</v>
       </c>
       <c r="R11" t="n">
-        <v>6538655</v>
+        <v>6538600</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1771,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -1341,45 +1341,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131648688</v>
+        <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>97903</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471211</v>
+        <v>471235</v>
       </c>
       <c r="R8" t="n">
-        <v>6538655</v>
+        <v>6538598</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1426,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,47 +1458,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B9" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1497,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R9" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,38 +1575,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647499</v>
+        <v>131647812</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>57090</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1614,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471235</v>
+        <v>471182</v>
       </c>
       <c r="R10" t="n">
-        <v>6538598</v>
+        <v>6538683</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,12 +1669,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,50 +1701,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647594</v>
+        <v>131648688</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>97903</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471229</v>
+        <v>471211</v>
       </c>
       <c r="R11" t="n">
-        <v>6538600</v>
+        <v>6538655</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -1341,50 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647499</v>
+        <v>131648688</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>97903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471235</v>
+        <v>471211</v>
       </c>
       <c r="R8" t="n">
-        <v>6538598</v>
+        <v>6538655</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,38 +1448,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647594</v>
+        <v>131647812</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57090</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1498,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471182</v>
       </c>
       <c r="R9" t="n">
-        <v>6538600</v>
+        <v>6538683</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,47 +1574,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647812</v>
+        <v>131647499</v>
       </c>
       <c r="B10" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471182</v>
+        <v>471235</v>
       </c>
       <c r="R10" t="n">
-        <v>6538683</v>
+        <v>6538598</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1659,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,45 +1691,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131648688</v>
+        <v>131647594</v>
       </c>
       <c r="B11" t="n">
-        <v>97903</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471211</v>
+        <v>471229</v>
       </c>
       <c r="R11" t="n">
-        <v>6538655</v>
+        <v>6538600</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1771,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -1341,45 +1341,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131648688</v>
+        <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>97903</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471211</v>
+        <v>471235</v>
       </c>
       <c r="R8" t="n">
-        <v>6538655</v>
+        <v>6538598</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1426,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,47 +1458,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B9" t="n">
-        <v>57090</v>
+        <v>57899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1497,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R9" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,50 +1575,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647499</v>
+        <v>131648688</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>97903</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471235</v>
+        <v>471211</v>
       </c>
       <c r="R10" t="n">
-        <v>6538598</v>
+        <v>6538655</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,7 +1645,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,12 +1655,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,38 +1682,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647594</v>
+        <v>131647812</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57090</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471229</v>
+        <v>471182</v>
       </c>
       <c r="R11" t="n">
-        <v>6538600</v>
+        <v>6538683</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648085</v>
+        <v>131648006</v>
       </c>
       <c r="B5" t="n">
-        <v>97903</v>
+        <v>97912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471169</v>
+        <v>471183</v>
       </c>
       <c r="R5" t="n">
-        <v>6538704</v>
+        <v>6538699</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B6" t="n">
-        <v>97906</v>
+        <v>97909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R6" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97906</v>
+        <v>97912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,50 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647499</v>
+        <v>131648688</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>97909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471235</v>
+        <v>471211</v>
       </c>
       <c r="R8" t="n">
-        <v>6538598</v>
+        <v>6538655</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,38 +1448,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647594</v>
+        <v>131647812</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1498,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471182</v>
       </c>
       <c r="R9" t="n">
-        <v>6538600</v>
+        <v>6538683</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,45 +1574,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131648688</v>
+        <v>131647499</v>
       </c>
       <c r="B10" t="n">
-        <v>97903</v>
+        <v>57901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471211</v>
+        <v>471235</v>
       </c>
       <c r="R10" t="n">
-        <v>6538655</v>
+        <v>6538598</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1645,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1655,7 +1659,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,47 +1691,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B11" t="n">
-        <v>57090</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R11" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>97912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,45 +1010,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B5" t="n">
-        <v>97912</v>
+        <v>57901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R5" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,45 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>97912</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R4" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,50 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>97912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R5" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1448,47 +1448,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647812</v>
+        <v>131647499</v>
       </c>
       <c r="B9" t="n">
-        <v>57092</v>
+        <v>57901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1497,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471182</v>
+        <v>471235</v>
       </c>
       <c r="R9" t="n">
-        <v>6538683</v>
+        <v>6538598</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1533,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,7 +1565,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647499</v>
+        <v>131647594</v>
       </c>
       <c r="B10" t="n">
         <v>57901</v>
@@ -1614,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471235</v>
+        <v>471229</v>
       </c>
       <c r="R10" t="n">
-        <v>6538598</v>
+        <v>6538600</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1650,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1691,38 +1682,47 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647594</v>
+        <v>131647812</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>57092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471229</v>
+        <v>471182</v>
       </c>
       <c r="R11" t="n">
-        <v>6538600</v>
+        <v>6538683</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,45 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>97912</v>
+        <v>57901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R4" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,50 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B5" t="n">
-        <v>57901</v>
+        <v>97912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R5" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1448,38 +1448,47 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647499</v>
+        <v>131647812</v>
       </c>
       <c r="B9" t="n">
-        <v>57901</v>
+        <v>57092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1488,10 +1497,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471235</v>
+        <v>471182</v>
       </c>
       <c r="R9" t="n">
-        <v>6538598</v>
+        <v>6538683</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1523,7 +1532,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,12 +1542,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,7 +1574,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647594</v>
+        <v>131647499</v>
       </c>
       <c r="B10" t="n">
         <v>57901</v>
@@ -1605,10 +1614,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471229</v>
+        <v>471235</v>
       </c>
       <c r="R10" t="n">
-        <v>6538600</v>
+        <v>6538598</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1640,7 +1649,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,7 +1659,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1682,47 +1691,38 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B11" t="n">
-        <v>57092</v>
+        <v>57901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R11" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>131647724</v>
       </c>
       <c r="B3" t="n">
-        <v>5198</v>
+        <v>5199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B4" t="n">
-        <v>57901</v>
+        <v>97915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B5" t="n">
         <v>97912</v>
@@ -1031,16 +1021,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R5" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,45 +1117,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B6" t="n">
-        <v>97909</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R6" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97912</v>
+        <v>97915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,45 +1341,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131648688</v>
+        <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>97909</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471211</v>
+        <v>471235</v>
       </c>
       <c r="R8" t="n">
-        <v>6538655</v>
+        <v>6538598</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1426,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,47 +1458,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B9" t="n">
-        <v>57092</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1497,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R9" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1532,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1542,12 +1543,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,38 +1575,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647499</v>
+        <v>131647812</v>
       </c>
       <c r="B10" t="n">
-        <v>57901</v>
+        <v>57095</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1614,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471235</v>
+        <v>471182</v>
       </c>
       <c r="R10" t="n">
-        <v>6538598</v>
+        <v>6538683</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1649,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,12 +1669,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,50 +1701,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647594</v>
+        <v>131648688</v>
       </c>
       <c r="B11" t="n">
-        <v>57901</v>
+        <v>97912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471229</v>
+        <v>471211</v>
       </c>
       <c r="R11" t="n">
-        <v>6538600</v>
+        <v>6538655</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B4" t="n">
-        <v>97915</v>
+        <v>97917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,16 +914,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -938,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R4" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,45 +1010,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B5" t="n">
-        <v>97912</v>
+        <v>57909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R5" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1080,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1090,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,50 +1127,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>97920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R6" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97915</v>
+        <v>97920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>131647594</v>
       </c>
       <c r="B9" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>131647812</v>
       </c>
       <c r="B10" t="n">
-        <v>57095</v>
+        <v>57100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>131648688</v>
       </c>
       <c r="B11" t="n">
-        <v>97912</v>
+        <v>97917</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,45 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>97917</v>
+        <v>57911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R4" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,50 +1020,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131647743</v>
+        <v>131648085</v>
       </c>
       <c r="B5" t="n">
-        <v>57909</v>
+        <v>97919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471233</v>
+        <v>471169</v>
       </c>
       <c r="R5" t="n">
-        <v>6538625</v>
+        <v>6538704</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,12 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1130,7 @@
         <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>97920</v>
+        <v>97922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97920</v>
+        <v>97922</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,50 +1341,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647499</v>
+        <v>131648688</v>
       </c>
       <c r="B8" t="n">
-        <v>57909</v>
+        <v>97919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471235</v>
+        <v>471211</v>
       </c>
       <c r="R8" t="n">
-        <v>6538598</v>
+        <v>6538655</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647594</v>
+        <v>131647499</v>
       </c>
       <c r="B9" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1498,10 +1488,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471235</v>
       </c>
       <c r="R9" t="n">
-        <v>6538600</v>
+        <v>6538598</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1575,47 +1565,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B10" t="n">
-        <v>57100</v>
+        <v>57911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R10" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1640,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1650,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131648688</v>
+        <v>131647812</v>
       </c>
       <c r="B11" t="n">
-        <v>97917</v>
+        <v>57102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,34 +1693,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471211</v>
+        <v>471182</v>
       </c>
       <c r="R11" t="n">
-        <v>6538655</v>
+        <v>6538683</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1771,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57909</v>
+        <v>57911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57912</v>
+        <v>57914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B4" t="n">
-        <v>57911</v>
+        <v>97922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1127,45 +1117,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B6" t="n">
-        <v>97922</v>
+        <v>57911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R6" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,45 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>97922</v>
+        <v>57911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R4" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1117,50 +1127,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>57911</v>
+        <v>97922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R6" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1341,45 +1341,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131648688</v>
+        <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>97919</v>
+        <v>57911</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471211</v>
+        <v>471235</v>
       </c>
       <c r="R8" t="n">
-        <v>6538655</v>
+        <v>6538598</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1426,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,7 +1458,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647499</v>
+        <v>131647594</v>
       </c>
       <c r="B9" t="n">
         <v>57911</v>
@@ -1488,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471235</v>
+        <v>471229</v>
       </c>
       <c r="R9" t="n">
-        <v>6538598</v>
+        <v>6538600</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1523,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1543,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1565,38 +1575,47 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647594</v>
+        <v>131647812</v>
       </c>
       <c r="B10" t="n">
-        <v>57911</v>
+        <v>57102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1605,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471229</v>
+        <v>471182</v>
       </c>
       <c r="R10" t="n">
-        <v>6538600</v>
+        <v>6538683</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1640,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1650,12 +1669,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131647812</v>
+        <v>131648688</v>
       </c>
       <c r="B11" t="n">
-        <v>57102</v>
+        <v>97919</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,48 +1712,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471182</v>
+        <v>471211</v>
       </c>
       <c r="R11" t="n">
-        <v>6538683</v>
+        <v>6538655</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1766,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,12 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:11</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648085</v>
+        <v>131648006</v>
       </c>
       <c r="B5" t="n">
-        <v>97919</v>
+        <v>97922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471169</v>
+        <v>471183</v>
       </c>
       <c r="R5" t="n">
-        <v>6538704</v>
+        <v>6538699</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B6" t="n">
-        <v>97922</v>
+        <v>97919</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R6" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1341,38 +1341,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647499</v>
+        <v>131647812</v>
       </c>
       <c r="B8" t="n">
-        <v>57911</v>
+        <v>57102</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1381,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471235</v>
+        <v>471182</v>
       </c>
       <c r="R8" t="n">
-        <v>6538598</v>
+        <v>6538683</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,12 +1435,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,7 +1467,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647594</v>
+        <v>131647499</v>
       </c>
       <c r="B9" t="n">
         <v>57911</v>
@@ -1498,10 +1507,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471235</v>
       </c>
       <c r="R9" t="n">
-        <v>6538600</v>
+        <v>6538598</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1575,47 +1584,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647812</v>
+        <v>131647594</v>
       </c>
       <c r="B10" t="n">
-        <v>57102</v>
+        <v>57911</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471182</v>
+        <v>471229</v>
       </c>
       <c r="R10" t="n">
-        <v>6538683</v>
+        <v>6538600</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B4" t="n">
-        <v>57911</v>
+        <v>97922</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1010,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648006</v>
+        <v>131648085</v>
       </c>
       <c r="B5" t="n">
-        <v>97922</v>
+        <v>97919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,16 +1021,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1055,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471183</v>
+        <v>471169</v>
       </c>
       <c r="R5" t="n">
-        <v>6538699</v>
+        <v>6538704</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,45 +1117,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B6" t="n">
-        <v>97919</v>
+        <v>57911</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R6" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1202,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647812</v>
+        <v>131648688</v>
       </c>
       <c r="B8" t="n">
-        <v>57102</v>
+        <v>97919</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,48 +1352,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471182</v>
+        <v>471211</v>
       </c>
       <c r="R8" t="n">
-        <v>6538683</v>
+        <v>6538655</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1425,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,12 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:11</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1701,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131648688</v>
+        <v>131647812</v>
       </c>
       <c r="B11" t="n">
-        <v>97919</v>
+        <v>57102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,34 +1693,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471211</v>
+        <v>471182</v>
       </c>
       <c r="R11" t="n">
-        <v>6538655</v>
+        <v>6538683</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1771,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1776,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,45 +903,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131648006</v>
+        <v>131647743</v>
       </c>
       <c r="B4" t="n">
-        <v>97922</v>
+        <v>57911</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471183</v>
+        <v>471233</v>
       </c>
       <c r="R4" t="n">
-        <v>6538699</v>
+        <v>6538625</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -973,7 +978,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +988,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1117,50 +1127,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131647743</v>
+        <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>57911</v>
+        <v>97922</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471233</v>
+        <v>471183</v>
       </c>
       <c r="R6" t="n">
-        <v>6538625</v>
+        <v>6538699</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1192,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,12 +1207,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -903,50 +903,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131648085</v>
       </c>
       <c r="B4" t="n">
-        <v>57911</v>
+        <v>97955</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471169</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538704</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +973,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +983,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,45 +1010,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B5" t="n">
-        <v>97919</v>
+        <v>57945</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R5" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1130,7 @@
         <v>131648006</v>
       </c>
       <c r="B6" t="n">
-        <v>97922</v>
+        <v>97958</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>131648678</v>
       </c>
       <c r="B7" t="n">
-        <v>97922</v>
+        <v>97958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,45 +1341,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131648688</v>
+        <v>131647499</v>
       </c>
       <c r="B8" t="n">
-        <v>97919</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471211</v>
+        <v>471235</v>
       </c>
       <c r="R8" t="n">
-        <v>6538655</v>
+        <v>6538598</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1426,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,50 +1458,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647499</v>
+        <v>131648688</v>
       </c>
       <c r="B9" t="n">
-        <v>57911</v>
+        <v>97955</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471235</v>
+        <v>471211</v>
       </c>
       <c r="R9" t="n">
-        <v>6538598</v>
+        <v>6538655</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1523,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,12 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,7 +1568,7 @@
         <v>131647594</v>
       </c>
       <c r="B10" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>131647812</v>
       </c>
       <c r="B11" t="n">
-        <v>57102</v>
+        <v>57136</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>131648564</v>
       </c>
       <c r="B12" t="n">
-        <v>57911</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>131647894</v>
       </c>
       <c r="B13" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131647961</v>
       </c>
       <c r="B14" t="n">
-        <v>57914</v>
+        <v>57948</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>129207591</v>
       </c>
       <c r="B2" t="n">
-        <v>92899</v>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131647724</v>
+        <v>131647499</v>
       </c>
       <c r="B3" t="n">
-        <v>5199</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,16 +820,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471234</v>
+        <v>471235</v>
       </c>
       <c r="R3" t="n">
-        <v>6538627</v>
+        <v>6538598</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -861,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kläckhål och gnag</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,14 +908,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131647743</v>
+        <v>131647594</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -943,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471233</v>
+        <v>471229</v>
       </c>
       <c r="R4" t="n">
-        <v>6538625</v>
+        <v>6538600</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -978,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,12 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av stående död gran</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131648085</v>
+        <v>131647743</v>
       </c>
       <c r="B5" t="n">
-        <v>97960</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,34 +1036,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471169</v>
+        <v>471233</v>
       </c>
       <c r="R5" t="n">
-        <v>6538704</v>
+        <v>6538625</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1090,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av stående död gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131648006</v>
+        <v>131648419</v>
       </c>
       <c r="B6" t="n">
-        <v>97963</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471183</v>
+        <v>471229</v>
       </c>
       <c r="R6" t="n">
-        <v>6538699</v>
+        <v>6538795</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1197,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1227,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131648678</v>
+        <v>131648564</v>
       </c>
       <c r="B7" t="n">
-        <v>97963</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471211</v>
+        <v>471253</v>
       </c>
       <c r="R7" t="n">
-        <v>6538658</v>
+        <v>6538764</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1304,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen av död avbruten gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131647499</v>
+        <v>131647894</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1352,16 +1387,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1381,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471235</v>
+        <v>471180</v>
       </c>
       <c r="R8" t="n">
-        <v>6538598</v>
+        <v>6538698</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,12 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt med färska ringhack på hela tallen, märkt med rött band</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,10 +1493,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131647594</v>
+        <v>131647961</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57975</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,16 +1504,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1498,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471229</v>
+        <v>471176</v>
       </c>
       <c r="R9" t="n">
-        <v>6538600</v>
+        <v>6538685</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1533,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,12 +1578,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Rikligt med ringhack med savflöde på tall märkt med rött märkband</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,47 +1610,38 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131647812</v>
+        <v>131648374</v>
       </c>
       <c r="B10" t="n">
-        <v>57136</v>
+        <v>57975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1624,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471182</v>
+        <v>471224</v>
       </c>
       <c r="R10" t="n">
-        <v>6538683</v>
+        <v>6538790</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1659,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1695,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Satt I träd och flög norrut.</t>
+          <t>Äldre ringhack på död tall. Barken har delvis fallit av men ringhacken syns högre upp där barken sitter kvar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131648688</v>
+        <v>131647812</v>
       </c>
       <c r="B11" t="n">
-        <v>97960</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,34 +1738,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471211</v>
+        <v>471182</v>
       </c>
       <c r="R11" t="n">
-        <v>6538655</v>
+        <v>6538683</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1771,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1821,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Satt I träd och flög norrut.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,38 +1853,38 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131648564</v>
+        <v>131648841</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>57162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1848,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471253</v>
+        <v>471164</v>
       </c>
       <c r="R12" t="n">
-        <v>6538764</v>
+        <v>6538505</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1883,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,12 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre födohack vid basen av död avbruten gran</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,27 +1965,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131647894</v>
+        <v>131647724</v>
       </c>
       <c r="B13" t="n">
-        <v>57948</v>
+        <v>5201</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1954,21 +1994,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471180</v>
+        <v>471234</v>
       </c>
       <c r="R13" t="n">
-        <v>6538698</v>
+        <v>6538627</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2000,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,12 +2045,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt med färska ringhack på hela tallen, märkt med rött band</t>
+          <t>Kläckhål och gnag</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,50 +2077,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131647961</v>
+        <v>131648085</v>
       </c>
       <c r="B14" t="n">
-        <v>57948</v>
+        <v>98060</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Spångmossen, Spångmossen, Vg</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471176</v>
+        <v>471169</v>
       </c>
       <c r="R14" t="n">
-        <v>6538685</v>
+        <v>6538704</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2117,7 +2147,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,12 +2157,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med ringhack med savflöde på tall märkt med rött märkband</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,6 +2181,434 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131648477</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>471204</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6538782</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131648688</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>471211</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6538655</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131648006</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>471183</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6538699</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131648678</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spångmossen, Spångmossen, Vg</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>471211</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6538658</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50765-2022 artfynd.xlsx
+++ b/artfynd/A 50765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129207591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647499</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647594</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1139,6 +1159,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1256,6 +1281,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648419</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1373,6 +1403,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648564</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1490,6 +1525,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647894</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1607,6 +1647,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647961</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1724,6 +1769,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648374</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1850,6 +1900,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647812</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1962,6 +2017,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648841</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2074,6 +2134,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131647724</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2181,6 +2246,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648085</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2288,6 +2358,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648477</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2395,6 +2470,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648688</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648006</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2609,8 +2694,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131648678</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>